--- a/anova_table.xlsx
+++ b/anova_table.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\showalt_d\Documents\GitHub\Apiary_LRR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6CF7157-6249-4CF0-90A5-41169435C050}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EFF33C4-7B47-4027-A8EF-2F2663657E70}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="3165" activeTab="2" xr2:uid="{3AAE0910-517F-4774-AF8D-3B09DF664141}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="3165" xr2:uid="{3AAE0910-517F-4774-AF8D-3B09DF664141}"/>
   </bookViews>
   <sheets>
     <sheet name="test_statistics" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="30">
   <si>
     <t>Source</t>
   </si>
@@ -114,6 +114,9 @@
   </si>
   <si>
     <t>test statistic: random effect of block= LRT; fixed effect of treatment = F</t>
+  </si>
+  <si>
+    <t>note CW25 block 1 removed from early annual total mortlity as a high outlier</t>
   </si>
 </sst>
 </file>
@@ -196,14 +199,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -518,7 +521,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98BF5774-CC3F-47FB-B6DB-43F70BC8900D}">
-  <dimension ref="B2:Q13"/>
+  <dimension ref="B2:Q14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="23.28515625" customWidth="1"/>
@@ -528,42 +531,42 @@
     <col min="6" max="6" width="1.85546875" customWidth="1"/>
     <col min="7" max="7" width="4.28515625" customWidth="1"/>
     <col min="8" max="8" width="10" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="2.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.85546875" customWidth="1"/>
     <col min="10" max="10" width="2.28515625" customWidth="1"/>
     <col min="11" max="11" width="4.5703125" customWidth="1"/>
     <col min="12" max="12" width="10" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="2.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.140625" customWidth="1"/>
     <col min="14" max="14" width="1.7109375" customWidth="1"/>
     <col min="15" max="15" width="4.7109375" customWidth="1"/>
     <col min="16" max="16" width="10" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="3" customWidth="1"/>
+    <col min="17" max="17" width="6.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:17" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="3"/>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
       <c r="F2" s="4"/>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
       <c r="J2" s="4"/>
-      <c r="K2" s="5" t="s">
+      <c r="K2" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="L2" s="5"/>
-      <c r="M2" s="5"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="10"/>
       <c r="N2" s="4"/>
-      <c r="O2" s="5" t="s">
+      <c r="O2" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="P2" s="5"/>
-      <c r="Q2" s="5"/>
+      <c r="P2" s="10"/>
+      <c r="Q2" s="10"/>
     </row>
     <row r="3" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
@@ -607,7 +610,7 @@
       </c>
     </row>
     <row r="4" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C4" s="3"/>
@@ -639,11 +642,14 @@
       <c r="E5">
         <v>0.29160000000000003</v>
       </c>
-      <c r="G5" t="s">
-        <v>3</v>
-      </c>
-      <c r="I5" t="s">
-        <v>3</v>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
       </c>
       <c r="K5" t="s">
         <v>3</v>
@@ -671,14 +677,14 @@
       <c r="E6">
         <v>7.9900000000000006E-3</v>
       </c>
-      <c r="G6" t="s">
-        <v>3</v>
-      </c>
-      <c r="H6" t="s">
-        <v>3</v>
-      </c>
-      <c r="I6" t="s">
-        <v>3</v>
+      <c r="G6">
+        <v>3</v>
+      </c>
+      <c r="H6">
+        <v>6.2549999999999999</v>
+      </c>
+      <c r="I6">
+        <v>4.7000000000000002E-3</v>
       </c>
       <c r="K6" t="s">
         <v>3</v>
@@ -706,8 +712,8 @@
       <c r="C7">
         <v>13</v>
       </c>
-      <c r="G7" t="s">
-        <v>3</v>
+      <c r="G7">
+        <v>17</v>
       </c>
       <c r="K7" t="s">
         <v>3</v>
@@ -717,7 +723,7 @@
       </c>
     </row>
     <row r="8" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C8" s="3"/>
@@ -749,11 +755,14 @@
       <c r="E9">
         <v>0.43120000000000003</v>
       </c>
-      <c r="G9" t="s">
-        <v>3</v>
-      </c>
-      <c r="I9" t="s">
-        <v>3</v>
+      <c r="G9">
+        <v>1</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>1</v>
       </c>
       <c r="K9" t="s">
         <v>3</v>
@@ -781,14 +790,14 @@
       <c r="E10">
         <v>0.253</v>
       </c>
-      <c r="G10" t="s">
-        <v>3</v>
-      </c>
-      <c r="H10" t="s">
-        <v>3</v>
-      </c>
-      <c r="I10" t="s">
-        <v>3</v>
+      <c r="G10">
+        <v>2</v>
+      </c>
+      <c r="H10">
+        <v>2.7469999999999999</v>
+      </c>
+      <c r="I10">
+        <v>0.1012</v>
       </c>
       <c r="K10" t="s">
         <v>3</v>
@@ -819,8 +828,8 @@
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
-      <c r="G11" s="1" t="s">
-        <v>3</v>
+      <c r="G11" s="1">
+        <v>13</v>
       </c>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
@@ -840,6 +849,11 @@
     <row r="13" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B14" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -899,7 +913,7 @@
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C4" s="3"/>
@@ -917,6 +931,9 @@
       <c r="C5">
         <v>4.7399999999999998E-2</v>
       </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
@@ -925,6 +942,9 @@
       <c r="C6">
         <v>6.2799999999999995E-2</v>
       </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
@@ -933,6 +953,9 @@
       <c r="C7">
         <v>-0.18559999999999999</v>
       </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
@@ -941,6 +964,9 @@
       <c r="C8">
         <v>-7.0099999999999996E-2</v>
       </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
@@ -949,9 +975,12 @@
       <c r="C9">
         <v>0.14549999999999999</v>
       </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C10" s="3"/>
@@ -966,43 +995,57 @@
       <c r="B11" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="8">
+      <c r="C11" s="7">
         <v>0.15529999999999999</v>
+      </c>
+      <c r="E11" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>23</v>
       </c>
-      <c r="C12" s="8">
+      <c r="C12" s="7">
         <v>4.9239999999999999E-2</v>
+      </c>
+      <c r="E12" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>24</v>
       </c>
-      <c r="C13" s="8">
+      <c r="C13" s="7">
         <v>1.5949999999999999E-2</v>
+      </c>
+      <c r="E13" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>25</v>
       </c>
-      <c r="C14" s="8">
+      <c r="C14" s="7">
         <v>-7.3709999999999998E-2</v>
+      </c>
+      <c r="E14" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B15" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C15" s="9">
+      <c r="C15" s="8">
         <v>-0.14679</v>
       </c>
       <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
+      <c r="E15" s="1">
+        <v>0</v>
+      </c>
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
@@ -1015,80 +1058,64 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E239B243-56EB-4F4B-9694-8B3990C51D61}">
-  <dimension ref="B2:Q12"/>
+  <dimension ref="B2:M12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="6" max="6" width="1.7109375" customWidth="1"/>
-    <col min="10" max="10" width="1.28515625" customWidth="1"/>
-    <col min="14" max="14" width="1.5703125" customWidth="1"/>
+    <col min="5" max="5" width="1.7109375" customWidth="1"/>
+    <col min="8" max="8" width="1.28515625" customWidth="1"/>
+    <col min="11" max="11" width="1.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="3"/>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="5" t="s">
+      <c r="D2" s="10"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="4"/>
-      <c r="K2" s="5" t="s">
+      <c r="G2" s="10"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="L2" s="5"/>
-      <c r="M2" s="5"/>
-      <c r="N2" s="4"/>
-      <c r="O2" s="5" t="s">
+      <c r="J2" s="10"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="P2" s="5"/>
-      <c r="Q2" s="5"/>
-    </row>
-    <row r="3" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="M2" s="10"/>
+    </row>
+    <row r="3" spans="2:13" x14ac:dyDescent="0.25">
       <c r="C3" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="3" t="s">
-        <v>1</v>
+      <c r="F3" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="G3" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="J3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="I3" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="K3" s="3" t="s">
+      <c r="L3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="M3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="M3" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="O3" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="P3" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q3" s="3" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B4" s="6" t="s">
+    </row>
+    <row r="4" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B4" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C4" s="3"/>
@@ -1102,12 +1129,8 @@
       <c r="K4" s="3"/>
       <c r="L4" s="3"/>
       <c r="M4" s="3"/>
-      <c r="N4" s="3"/>
-      <c r="O4" s="3"/>
-      <c r="P4" s="3"/>
-      <c r="Q4" s="3"/>
-    </row>
-    <row r="5" spans="2:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>17</v>
       </c>
@@ -1117,11 +1140,14 @@
       <c r="D5">
         <v>0.17299999999999999</v>
       </c>
-      <c r="E5" s="7">
-        <v>7.192E-9</v>
-      </c>
-    </row>
-    <row r="6" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="F5">
+        <v>2.07E-2</v>
+      </c>
+      <c r="G5">
+        <v>1E-4</v>
+      </c>
+    </row>
+    <row r="6" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>18</v>
       </c>
@@ -1131,11 +1157,14 @@
       <c r="D6">
         <v>0.1376</v>
       </c>
-      <c r="E6" s="7">
-        <v>1.0332999999999999E-9</v>
-      </c>
-    </row>
-    <row r="7" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="F6">
+        <v>1.3299999999999999E-2</v>
+      </c>
+      <c r="G6">
+        <v>1E-4</v>
+      </c>
+    </row>
+    <row r="7" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>19</v>
       </c>
@@ -1145,11 +1174,14 @@
       <c r="D7">
         <v>0.1376</v>
       </c>
-      <c r="E7" s="7">
-        <v>6.5840000000000002E-10</v>
-      </c>
-    </row>
-    <row r="8" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="F7">
+        <v>7.4999999999999997E-3</v>
+      </c>
+      <c r="G7">
+        <v>1E-4</v>
+      </c>
+    </row>
+    <row r="8" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>20</v>
       </c>
@@ -1159,12 +1191,15 @@
       <c r="D8">
         <v>0.1376</v>
       </c>
-      <c r="E8" s="7">
-        <v>1.804E-7</v>
-      </c>
-    </row>
-    <row r="9" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B9" s="6" t="s">
+      <c r="F8">
+        <v>1.41E-2</v>
+      </c>
+      <c r="G8">
+        <v>1E-4</v>
+      </c>
+    </row>
+    <row r="9" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B9" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C9" s="3"/>
@@ -1178,40 +1213,42 @@
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
       <c r="M9" s="3"/>
-      <c r="N9" s="3"/>
-      <c r="O9" s="3"/>
-      <c r="P9" s="3"/>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="2:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="8">
+      <c r="C10" s="7">
         <v>1.1994</v>
       </c>
-      <c r="D10" s="8">
+      <c r="D10" s="7">
         <v>0.15440000000000001</v>
       </c>
-      <c r="E10" s="7">
-        <v>3.2899999999999998E-6</v>
-      </c>
-    </row>
-    <row r="11" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="F10" s="7">
+        <v>2.52E-2</v>
+      </c>
+      <c r="G10" s="6">
+        <v>3.2100000000000001E-5</v>
+      </c>
+    </row>
+    <row r="11" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>18</v>
       </c>
       <c r="C11">
         <v>1.3070999999999999</v>
       </c>
-      <c r="D11" s="8">
+      <c r="D11" s="7">
         <v>0.1227</v>
       </c>
-      <c r="E11" s="7">
-        <v>3.4499999999999998E-7</v>
-      </c>
-    </row>
-    <row r="12" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="F11" s="7">
+        <v>2.1399999999999999E-2</v>
+      </c>
+      <c r="G11" s="6">
+        <v>1.9199999999999999E-5</v>
+      </c>
+    </row>
+    <row r="12" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B12" s="1" t="s">
         <v>27</v>
       </c>
@@ -1221,28 +1258,26 @@
       <c r="D12" s="1">
         <v>0.1227</v>
       </c>
-      <c r="E12" s="10">
-        <v>8.5700000000000006E-8</v>
-      </c>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1">
+        <v>2.0299999999999999E-2</v>
+      </c>
+      <c r="G12" s="9">
+        <v>1.9199999999999999E-5</v>
+      </c>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
-      <c r="N12" s="1"/>
-      <c r="O12" s="1"/>
-      <c r="P12" s="1"/>
-      <c r="Q12" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="C2:E2"/>
-    <mergeCell ref="G2:I2"/>
-    <mergeCell ref="K2:M2"/>
-    <mergeCell ref="O2:Q2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="L2:M2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/anova_table.xlsx
+++ b/anova_table.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\showalt_d\Documents\GitHub\Apiary_LRR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EFF33C4-7B47-4027-A8EF-2F2663657E70}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{047E534A-5113-496F-B4CE-24BFA7A98B96}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="3165" xr2:uid="{3AAE0910-517F-4774-AF8D-3B09DF664141}"/>
   </bookViews>
   <sheets>
     <sheet name="test_statistics" sheetId="1" r:id="rId1"/>
     <sheet name="Block_intercepts" sheetId="3" r:id="rId2"/>
-    <sheet name="TRT_lsmeans" sheetId="2" r:id="rId3"/>
+    <sheet name="TRT_means" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="32">
   <si>
     <t>Source</t>
   </si>
@@ -38,9 +38,6 @@
     <t>df</t>
   </si>
   <si>
-    <t>#</t>
-  </si>
-  <si>
     <t>Error</t>
   </si>
   <si>
@@ -117,6 +114,15 @@
   </si>
   <si>
     <t>note CW25 block 1 removed from early annual total mortlity as a high outlier</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>LATE</t>
+  </si>
+  <si>
+    <t>Late time period means for all variables are measured means, annual total mortality means for early and mid time periods, and suppression mortality for mid time period are estimated marginal means, all others are least-squares means</t>
   </si>
 </sst>
 </file>
@@ -189,7 +195,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -207,6 +213,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -535,35 +543,35 @@
     <col min="10" max="10" width="2.28515625" customWidth="1"/>
     <col min="11" max="11" width="4.5703125" customWidth="1"/>
     <col min="12" max="12" width="10" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="6.140625" customWidth="1"/>
+    <col min="13" max="13" width="7.140625" customWidth="1"/>
     <col min="14" max="14" width="1.7109375" customWidth="1"/>
     <col min="15" max="15" width="4.7109375" customWidth="1"/>
     <col min="16" max="16" width="10" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="6.42578125" customWidth="1"/>
+    <col min="17" max="17" width="7.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:17" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="3"/>
       <c r="C2" s="10" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D2" s="10"/>
       <c r="E2" s="10"/>
       <c r="F2" s="4"/>
       <c r="G2" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H2" s="10"/>
       <c r="I2" s="10"/>
       <c r="J2" s="4"/>
       <c r="K2" s="10" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L2" s="10"/>
       <c r="M2" s="10"/>
       <c r="N2" s="4"/>
       <c r="O2" s="10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P2" s="10"/>
       <c r="Q2" s="10"/>
@@ -576,7 +584,7 @@
         <v>2</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>1</v>
@@ -585,7 +593,7 @@
         <v>2</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>1</v>
@@ -594,7 +602,7 @@
         <v>2</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M3" s="3" t="s">
         <v>1</v>
@@ -603,7 +611,7 @@
         <v>2</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Q3" s="3" t="s">
         <v>1</v>
@@ -611,7 +619,7 @@
     </row>
     <row r="4" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B4" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
@@ -631,7 +639,7 @@
     </row>
     <row r="5" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -642,31 +650,28 @@
       <c r="E5">
         <v>0.29160000000000003</v>
       </c>
-      <c r="G5">
+      <c r="K5">
         <v>1</v>
       </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
+      <c r="L5">
+        <v>6.4922000000000004</v>
+      </c>
+      <c r="M5" s="11">
+        <v>1.0800000000000001E-2</v>
+      </c>
+      <c r="O5">
         <v>1</v>
       </c>
-      <c r="K5" t="s">
-        <v>3</v>
-      </c>
-      <c r="M5" t="s">
-        <v>3</v>
-      </c>
-      <c r="O5" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>3</v>
+      <c r="P5">
+        <v>3.0167999999999999</v>
+      </c>
+      <c r="Q5">
+        <v>8.2409999999999997E-2</v>
       </c>
     </row>
     <row r="6" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C6">
         <v>3</v>
@@ -674,7 +679,7 @@
       <c r="D6">
         <v>6.0979000000000001</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="11">
         <v>7.9900000000000006E-3</v>
       </c>
       <c r="G6">
@@ -683,48 +688,48 @@
       <c r="H6">
         <v>6.2549999999999999</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="11">
         <v>4.7000000000000002E-3</v>
       </c>
-      <c r="K6" t="s">
+      <c r="K6">
         <v>3</v>
       </c>
-      <c r="L6" t="s">
+      <c r="L6">
+        <v>5.8109999999999999</v>
+      </c>
+      <c r="M6" s="11">
+        <v>9.2999999999999992E-3</v>
+      </c>
+      <c r="O6">
         <v>3</v>
       </c>
-      <c r="M6" t="s">
-        <v>3</v>
-      </c>
-      <c r="O6" t="s">
-        <v>3</v>
-      </c>
-      <c r="P6" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>3</v>
+      <c r="P6">
+        <v>9.2687000000000008</v>
+      </c>
+      <c r="Q6" s="11">
+        <v>1.4430000000000001E-3</v>
       </c>
     </row>
     <row r="7" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C7">
         <v>13</v>
       </c>
       <c r="G7">
-        <v>17</v>
-      </c>
-      <c r="K7" t="s">
-        <v>3</v>
-      </c>
-      <c r="O7" t="s">
-        <v>3</v>
+        <v>13</v>
+      </c>
+      <c r="K7">
+        <v>13</v>
+      </c>
+      <c r="O7">
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B8" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
@@ -744,7 +749,7 @@
     </row>
     <row r="9" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -755,31 +760,19 @@
       <c r="E9">
         <v>0.43120000000000003</v>
       </c>
-      <c r="G9">
+      <c r="K9">
         <v>1</v>
       </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-      <c r="I9">
-        <v>1</v>
-      </c>
-      <c r="K9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M9" t="s">
-        <v>3</v>
-      </c>
-      <c r="O9" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>3</v>
+      <c r="L9">
+        <v>10.287000000000001</v>
+      </c>
+      <c r="M9" s="11">
+        <v>1.34E-3</v>
       </c>
     </row>
     <row r="10" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C10">
         <v>2</v>
@@ -799,28 +792,28 @@
       <c r="I10">
         <v>0.1012</v>
       </c>
-      <c r="K10" t="s">
-        <v>3</v>
-      </c>
-      <c r="L10" t="s">
-        <v>3</v>
-      </c>
-      <c r="M10" t="s">
-        <v>3</v>
-      </c>
-      <c r="O10" t="s">
-        <v>3</v>
-      </c>
-      <c r="P10" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>3</v>
+      <c r="K10">
+        <v>2</v>
+      </c>
+      <c r="L10">
+        <v>1.9691000000000001</v>
+      </c>
+      <c r="M10">
+        <v>0.20039999999999999</v>
+      </c>
+      <c r="O10">
+        <v>2</v>
+      </c>
+      <c r="P10">
+        <v>2.1128999999999998</v>
+      </c>
+      <c r="Q10">
+        <v>0.1716</v>
       </c>
     </row>
     <row r="11" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B11" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C11" s="1">
         <v>8</v>
@@ -829,31 +822,31 @@
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
       <c r="G11" s="1">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
-      <c r="K11" s="1" t="s">
-        <v>3</v>
+      <c r="K11" s="1">
+        <v>8</v>
       </c>
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
       <c r="N11" s="1"/>
-      <c r="O11" s="1" t="s">
-        <v>3</v>
+      <c r="O11" s="1">
+        <v>10</v>
       </c>
       <c r="P11" s="1"/>
       <c r="Q11" s="1"/>
     </row>
     <row r="13" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -883,38 +876,38 @@
     <row r="2" spans="2:9" ht="60" x14ac:dyDescent="0.25">
       <c r="B2" s="3"/>
       <c r="C2" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F2" s="4"/>
       <c r="G2" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H2" s="4"/>
       <c r="I2" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C3" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B4" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
@@ -926,62 +919,92 @@
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C5">
         <v>4.7399999999999998E-2</v>
       </c>
-      <c r="E5">
-        <v>0</v>
+      <c r="E5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G5">
+        <v>-1.2800000000000001E-2</v>
+      </c>
+      <c r="I5">
+        <v>1.3299999999999999E-2</v>
       </c>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C6">
         <v>6.2799999999999995E-2</v>
       </c>
-      <c r="E6">
-        <v>0</v>
+      <c r="E6" t="s">
+        <v>29</v>
+      </c>
+      <c r="G6">
+        <v>-6.1000000000000004E-3</v>
+      </c>
+      <c r="I6">
+        <v>-6.9999999999999999E-4</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C7">
         <v>-0.18559999999999999</v>
       </c>
-      <c r="E7">
-        <v>0</v>
+      <c r="E7" t="s">
+        <v>29</v>
+      </c>
+      <c r="G7">
+        <v>-1.2999999999999999E-2</v>
+      </c>
+      <c r="I7">
+        <v>1.18E-2</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C8">
         <v>-7.0099999999999996E-2</v>
       </c>
-      <c r="E8">
-        <v>0</v>
+      <c r="E8" t="s">
+        <v>29</v>
+      </c>
+      <c r="G8">
+        <v>-1.03E-2</v>
+      </c>
+      <c r="I8">
+        <v>6.4999999999999997E-3</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C9">
         <v>0.14549999999999999</v>
       </c>
-      <c r="E9">
-        <v>0</v>
+      <c r="E9" t="s">
+        <v>29</v>
+      </c>
+      <c r="G9">
+        <v>4.2099999999999999E-2</v>
+      </c>
+      <c r="I9">
+        <v>-3.09E-2</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B10" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
@@ -993,63 +1016,91 @@
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C11" s="7">
         <v>0.15529999999999999</v>
       </c>
-      <c r="E11" s="7">
-        <v>0</v>
+      <c r="E11" t="s">
+        <v>29</v>
+      </c>
+      <c r="G11" s="7">
+        <v>-1.7500000000000002E-2</v>
+      </c>
+      <c r="I11" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C12" s="7">
         <v>4.9239999999999999E-2</v>
       </c>
-      <c r="E12" s="7">
-        <v>0</v>
+      <c r="E12" t="s">
+        <v>29</v>
+      </c>
+      <c r="G12" s="7">
+        <v>-1.09E-2</v>
+      </c>
+      <c r="I12" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C13" s="7">
         <v>1.5949999999999999E-2</v>
       </c>
-      <c r="E13" s="7">
-        <v>0</v>
+      <c r="E13" t="s">
+        <v>29</v>
+      </c>
+      <c r="G13" s="7">
+        <v>4.4999999999999997E-3</v>
+      </c>
+      <c r="I13" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="14" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C14" s="7">
         <v>-7.3709999999999998E-2</v>
       </c>
-      <c r="E14" s="7">
-        <v>0</v>
+      <c r="E14" t="s">
+        <v>29</v>
+      </c>
+      <c r="G14" s="7">
+        <v>-1.38E-2</v>
+      </c>
+      <c r="I14" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="15" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B15" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C15" s="8">
         <v>-0.14679</v>
       </c>
       <c r="D15" s="1"/>
-      <c r="E15" s="1">
-        <v>0</v>
+      <c r="E15" s="1" t="s">
+        <v>29</v>
       </c>
       <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
+      <c r="G15" s="1">
+        <v>3.7600000000000001E-2</v>
+      </c>
       <c r="H15" s="1"/>
-      <c r="I15" s="1"/>
+      <c r="I15" s="1" t="s">
+        <v>29</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1058,7 +1109,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E239B243-56EB-4F4B-9694-8B3990C51D61}">
-  <dimension ref="B2:M12"/>
+  <dimension ref="B2:M16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="5" max="5" width="1.7109375" customWidth="1"/>
@@ -1066,57 +1117,57 @@
     <col min="11" max="11" width="1.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:13" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="3"/>
       <c r="C2" s="10" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D2" s="10"/>
       <c r="E2" s="4"/>
       <c r="F2" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G2" s="10"/>
       <c r="H2" s="4"/>
       <c r="I2" s="10" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J2" s="10"/>
       <c r="K2" s="4"/>
       <c r="L2" s="10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M2" s="10"/>
     </row>
     <row r="3" spans="2:13" x14ac:dyDescent="0.25">
       <c r="C3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="F3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="I3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J3" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="L3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="M3" s="3" t="s">
         <v>15</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="4" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B4" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
@@ -1132,7 +1183,7 @@
     </row>
     <row r="5" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C5">
         <v>1.7795000000000001</v>
@@ -1144,12 +1195,24 @@
         <v>2.07E-2</v>
       </c>
       <c r="G5">
-        <v>1E-4</v>
+        <v>2.0000000000000001E-4</v>
+      </c>
+      <c r="I5">
+        <v>7.1199999999999996E-3</v>
+      </c>
+      <c r="J5">
+        <v>2.9999999999999997E-4</v>
+      </c>
+      <c r="L5">
+        <v>8.9999999999999993E-3</v>
+      </c>
+      <c r="M5">
+        <v>2.9999999999999997E-4</v>
       </c>
     </row>
     <row r="6" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C6">
         <v>1.8213999999999999</v>
@@ -1163,10 +1226,22 @@
       <c r="G6">
         <v>1E-4</v>
       </c>
+      <c r="I6">
+        <v>4.47E-3</v>
+      </c>
+      <c r="J6">
+        <v>2.0000000000000001E-4</v>
+      </c>
+      <c r="L6">
+        <v>3.8E-3</v>
+      </c>
+      <c r="M6">
+        <v>2.0000000000000001E-4</v>
+      </c>
     </row>
     <row r="7" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C7">
         <v>1.881</v>
@@ -1180,10 +1255,22 @@
       <c r="G7">
         <v>1E-4</v>
       </c>
+      <c r="I7">
+        <v>5.1999999999999998E-3</v>
+      </c>
+      <c r="J7">
+        <v>2.0000000000000001E-4</v>
+      </c>
+      <c r="L7">
+        <v>9.9000000000000008E-3</v>
+      </c>
+      <c r="M7">
+        <v>2.0000000000000001E-4</v>
+      </c>
     </row>
     <row r="8" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C8">
         <v>1.2416</v>
@@ -1197,10 +1284,22 @@
       <c r="G8">
         <v>1E-4</v>
       </c>
+      <c r="I8">
+        <v>8.0999999999999996E-4</v>
+      </c>
+      <c r="J8">
+        <v>2.0000000000000001E-4</v>
+      </c>
+      <c r="L8">
+        <v>1.9800000000000002E-2</v>
+      </c>
+      <c r="M8">
+        <v>2.0000000000000001E-4</v>
+      </c>
     </row>
     <row r="9" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B9" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
@@ -1216,7 +1315,7 @@
     </row>
     <row r="10" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C10" s="7">
         <v>1.1994</v>
@@ -1228,12 +1327,24 @@
         <v>2.52E-2</v>
       </c>
       <c r="G10" s="6">
-        <v>3.2100000000000001E-5</v>
+        <v>4.1699999999999997E-5</v>
+      </c>
+      <c r="I10" s="7">
+        <v>9.5300000000000003E-3</v>
+      </c>
+      <c r="J10" s="7">
+        <v>1.2999999999999999E-4</v>
+      </c>
+      <c r="L10">
+        <v>7.1199999999999996E-3</v>
+      </c>
+      <c r="M10" s="6">
+        <v>1.35E-4</v>
       </c>
     </row>
     <row r="11" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C11">
         <v>1.3070999999999999</v>
@@ -1245,12 +1356,24 @@
         <v>2.1399999999999999E-2</v>
       </c>
       <c r="G11" s="6">
-        <v>1.9199999999999999E-5</v>
+        <v>2.5000000000000001E-5</v>
+      </c>
+      <c r="I11" s="7">
+        <v>7.3299999999999997E-3</v>
+      </c>
+      <c r="J11" s="7">
+        <v>1.1E-4</v>
+      </c>
+      <c r="L11">
+        <v>7.9900000000000006E-3</v>
+      </c>
+      <c r="M11" s="6">
+        <v>8.0900000000000001E-5</v>
       </c>
     </row>
     <row r="12" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B12" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C12" s="1">
         <v>1.4956</v>
@@ -1263,14 +1386,52 @@
         <v>2.0299999999999999E-2</v>
       </c>
       <c r="G12" s="9">
-        <v>1.9199999999999999E-5</v>
+        <v>2.5000000000000001E-5</v>
       </c>
       <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
-      <c r="J12" s="1"/>
+      <c r="I12" s="1">
+        <v>9.3299999999999998E-3</v>
+      </c>
+      <c r="J12" s="1">
+        <v>1.1E-4</v>
+      </c>
       <c r="K12" s="1"/>
-      <c r="L12" s="1"/>
-      <c r="M12" s="1"/>
+      <c r="L12" s="1">
+        <v>4.1399999999999996E-3</v>
+      </c>
+      <c r="M12" s="9">
+        <v>8.0900000000000001E-5</v>
+      </c>
+    </row>
+    <row r="13" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B13" s="12" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B14" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14" s="1">
+        <v>0.27033999999999997</v>
+      </c>
+      <c r="D14" s="1">
+        <v>0.23949146144278297</v>
+      </c>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1"/>
+      <c r="L14" s="1"/>
+      <c r="M14" s="1"/>
+    </row>
+    <row r="16" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
+        <v>31</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="4">

--- a/anova_table.xlsx
+++ b/anova_table.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="32">
   <si>
     <t xml:space="preserve">annual BA increment</t>
   </si>
@@ -71,9 +71,6 @@
   </si>
   <si>
     <t xml:space="preserve">*test statistic: random effect of block= LRT; fixed effect of treatment = F</t>
-  </si>
-  <si>
-    <t xml:space="preserve">note CW25 block 1 removed from early annual total mortlity as a high outlier</t>
   </si>
   <si>
     <t xml:space="preserve">annual LRR mortality</t>
@@ -344,7 +341,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B1:Q14"/>
-  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.70703125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="17.92"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="2.85"/>
@@ -353,8 +350,8 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="1.85"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="3.33"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="7.36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="6.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="2.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="6.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="2.31"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="4.57"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="7.64"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="7.15"/>
@@ -507,16 +504,16 @@
         <v>3</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>6.255</v>
+        <v>3.7098</v>
       </c>
       <c r="I6" s="8" t="n">
-        <v>0.0047</v>
+        <v>0.03741</v>
       </c>
       <c r="K6" s="0" t="n">
         <v>3</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>5.811</v>
+        <v>5.8112</v>
       </c>
       <c r="M6" s="8" t="n">
         <v>0.0093</v>
@@ -620,10 +617,10 @@
         <v>2</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>2.747</v>
+        <v>2.1129</v>
       </c>
       <c r="I10" s="0" t="n">
-        <v>0.1012</v>
+        <v>0.1716</v>
       </c>
       <c r="K10" s="0" t="n">
         <v>2</v>
@@ -638,10 +635,10 @@
         <v>2</v>
       </c>
       <c r="P10" s="0" t="n">
-        <v>2.1129</v>
+        <v>2.1071</v>
       </c>
       <c r="Q10" s="0" t="n">
-        <v>0.1716</v>
+        <v>0.1723</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -677,11 +674,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="0" t="s">
-        <v>16</v>
-      </c>
-    </row>
+    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="C2:E2"/>
@@ -705,12 +698,12 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:I15"/>
-  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.70703125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="11.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="11.3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="1.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="1.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="1.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="1.12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="11.71"/>
   </cols>
   <sheetData>
@@ -725,7 +718,7 @@
       </c>
       <c r="F2" s="3"/>
       <c r="G2" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H2" s="3"/>
       <c r="I2" s="2" t="s">
@@ -734,16 +727,16 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -760,7 +753,7 @@
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="0" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C5" s="0" t="n">
         <v>0.0474</v>
@@ -777,7 +770,7 @@
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="0" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C6" s="0" t="n">
         <v>0.0628</v>
@@ -794,7 +787,7 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="0" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C7" s="0" t="n">
         <v>-0.1856</v>
@@ -811,7 +804,7 @@
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="0" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C8" s="0" t="n">
         <v>-0.0701</v>
@@ -828,7 +821,7 @@
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="0" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C9" s="0" t="n">
         <v>0.1455</v>
@@ -857,7 +850,7 @@
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="0" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C11" s="12" t="n">
         <v>0.1553</v>
@@ -874,7 +867,7 @@
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="0" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C12" s="13" t="n">
         <v>0.04924</v>
@@ -891,7 +884,7 @@
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="0" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C13" s="13" t="n">
         <v>0.01595</v>
@@ -908,7 +901,7 @@
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="0" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C14" s="13" t="n">
         <v>-0.07371</v>
@@ -925,7 +918,7 @@
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C15" s="14" t="n">
         <v>-0.14679</v>
@@ -960,7 +953,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:M27"/>
-  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.70703125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="1.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="1.29"/>
@@ -980,7 +973,7 @@
       <c r="G2" s="2"/>
       <c r="H2" s="3"/>
       <c r="I2" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J2" s="2"/>
       <c r="K2" s="3"/>
@@ -991,28 +984,28 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>25</v>
-      </c>
       <c r="F3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="G3" s="1" t="s">
-        <v>25</v>
-      </c>
       <c r="I3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J3" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J3" s="1" t="s">
-        <v>25</v>
-      </c>
       <c r="L3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="M3" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1033,7 +1026,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="0" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C5" s="0" t="n">
         <v>1.7795</v>
@@ -1062,7 +1055,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="0" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C6" s="0" t="n">
         <v>1.8214</v>
@@ -1091,7 +1084,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>1.881</v>
@@ -1120,7 +1113,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="0" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C8" s="0" t="n">
         <v>1.2416</v>
@@ -1165,7 +1158,7 @@
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="0" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C10" s="13" t="n">
         <v>1.1994</v>
@@ -1194,7 +1187,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="0" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C11" s="0" t="n">
         <v>1.3071</v>
@@ -1223,7 +1216,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C12" s="10" t="n">
         <v>1.4956</v>
@@ -1255,12 +1248,12 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="23" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C14" s="22" t="n">
         <v>0.27034</v>
@@ -1292,7 +1285,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
